--- a/signal_coodination/summary_of_offsets_and_TTT.xlsx
+++ b/signal_coodination/summary_of_offsets_and_TTT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50a7229fe28fb870/デスクトップ/randy_utokyo/signal_coodination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9FF4265-3E83-4ECA-8FA0-277DFF0EECC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{D9FF4265-3E83-4ECA-8FA0-277DFF0EECC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6527141E-44F8-4917-BFD5-5A0A65DD5A72}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="22410" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B899796-BA45-4823-980F-3D7A2A852D6D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{4B899796-BA45-4823-980F-3D7A2A852D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -497,7 +497,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAB5F8FF-42A7-4150-A23E-4B8C1D524FFF}" name="ピボットテーブル1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAB5F8FF-42A7-4150-A23E-4B8C1D524FFF}" name="ピボットテーブル1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -927,6 +927,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21DD5F2-5E62-45E2-9391-88808761FB57}">
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="8" max="8" width="20.25" customWidth="1"/>
+    <col min="9" max="9" width="26.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
